--- a/Files List Error Tracking.xlsx
+++ b/Files List Error Tracking.xlsx
@@ -8,19 +8,42 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AppDev\DebitLens\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D7E03E24-364A-47FC-94DB-DDB00EF05D1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{63CDCEC1-4EAC-42A0-AFA6-37C4D4DF03E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{0EC2DA8C-4978-4A72-B938-F974F5269E45}"/>
+    <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" activeTab="1" xr2:uid="{0EC2DA8C-4978-4A72-B938-F974F5269E45}"/>
   </bookViews>
   <sheets>
-    <sheet name="Files List" sheetId="1" r:id="rId1"/>
+    <sheet name="Error List" sheetId="2" r:id="rId1"/>
+    <sheet name="Files List" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="88">
   <si>
     <t>AccountForm.tsx"</t>
   </si>
@@ -284,27 +307,6 @@
   </si>
   <si>
     <t>Errors</t>
-  </si>
-  <si>
-    <t>Property 'prefs' does not exist on type 'AppState'.
-Property 'prefs' does not exist on type 'AppState'.</t>
-  </si>
-  <si>
-    <t>Property 'label' does not exist on type 'Account'.
-Object literal may only specify known properties, and 'label' does not exist in type 'Partial&lt;Account&gt;'.</t>
-  </si>
-  <si>
-    <t>Property 'note' does not exist on type 'Transaction'.</t>
-  </si>
-  <si>
-    <t>Object literal may only specify known properties, and 'label' does not exist in type 'Partial&lt;Account&gt;'.</t>
-  </si>
-  <si>
-    <t>Module '"../state/AppContext"' has no exported member 'Budget'.
-Property 'budgets' does not exist on type 'AppState'.
-Property 'updateBudget' does not exist on type 'AppActions'.
-Property 'addBudget' does not exist on type 'AppActions'.
-Property 'deleteBudget' does not exist on type 'AppActions'.</t>
   </si>
 </sst>
 </file>
@@ -794,8 +796,15 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="0" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -1185,789 +1194,804 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C0B799D-B152-4EDC-90BC-C1450490B7CC}">
+  <dimension ref="A2:D17"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="114.5703125" style="3" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="str" cm="1">
+        <f t="array" ref="A2:D2">_xlfn._xlws.FILTER('Files List'!A:D, 'Files List'!D:D&lt;&gt;"")</f>
+        <v>Root Folder</v>
+      </c>
+      <c r="B2" s="2" t="str">
+        <v>Sub Folder</v>
+      </c>
+      <c r="C2" s="1" t="str">
+        <v>Files</v>
+      </c>
+      <c r="D2" s="2" t="str">
+        <v>Errors</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="30" x14ac:dyDescent="0.25"/>
+    <row r="4" spans="1:4" ht="30" x14ac:dyDescent="0.25"/>
+    <row r="7" spans="1:4" ht="75" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="1:4" ht="120" x14ac:dyDescent="0.25"/>
+    <row r="12" spans="1:4" ht="150" x14ac:dyDescent="0.25"/>
+    <row r="15" spans="1:4" ht="30" x14ac:dyDescent="0.25"/>
+    <row r="16" spans="1:4" ht="30" x14ac:dyDescent="0.25"/>
+    <row r="17" ht="60" x14ac:dyDescent="0.25"/>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B41C8E12-756B-4D03-AF8C-7EAD0401066F}">
   <dimension ref="A1:D68"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.7109375" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.7109375" style="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.140625" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="73.5703125" style="5" customWidth="1"/>
-    <col min="5" max="16384" width="9.140625" style="3"/>
+    <col min="1" max="1" width="22.7109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.7109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="73.5703125" style="8" customWidth="1"/>
+    <col min="5" max="16384" width="9.140625" style="6"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="5" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="B2" s="5" t="s">
+      <c r="A2" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="B2" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="8" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="B3" s="5" t="s">
+      <c r="A3" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="B3" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="8" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="B4" s="5" t="s">
+      <c r="A4" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="B4" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="8" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="B5" s="5" t="s">
+      <c r="A5" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="B5" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="8" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="B6" s="5" t="s">
+      <c r="A6" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="B6" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="8" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="B7" s="5" t="s">
+      <c r="A7" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="B7" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="8" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="B8" s="5" t="s">
+      <c r="A8" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="B8" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="8" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="B9" s="5" t="s">
+      <c r="A9" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="B9" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="8" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="B10" s="5" t="s">
+      <c r="A10" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="B10" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="8" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="B11" s="5" t="s">
+      <c r="A11" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="B11" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="8" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="B12" s="5" t="s">
+      <c r="A12" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="B12" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="8" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="B13" s="5" t="s">
+      <c r="A13" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="B13" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="8" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="B14" s="5" t="s">
+      <c r="A14" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="B14" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="8" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="B15" s="5" t="s">
+      <c r="A15" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="B15" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="C15" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="B16" s="5" t="s">
+      <c r="A16" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="B16" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C16" s="8" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="B17" s="5" t="s">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="B17" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C17" s="8" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="B18" s="5" t="s">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="B18" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C18" s="8" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="B19" s="5" t="s">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="B19" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="C19" s="8" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="B20" s="5" t="s">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="B20" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="C20" s="8" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="B21" s="5" t="s">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="B21" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="C21" s="8" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="B22" s="5" t="s">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="B22" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="C22" s="5" t="s">
+      <c r="C22" s="8" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="B23" s="5" t="s">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="B23" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="C23" s="5" t="s">
+      <c r="C23" s="8" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="B24" s="5" t="s">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="B24" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="C24" s="5" t="s">
+      <c r="C24" s="8" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A25" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="B25" s="5" t="s">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="B25" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="C25" s="5" t="s">
+      <c r="C25" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="D25" s="5" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" ht="45" x14ac:dyDescent="0.25">
-      <c r="A26" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="C26" s="5" t="s">
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="C26" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="D26" s="5" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="C27" s="5" t="s">
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="C27" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="D27" s="5" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A28" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="C28" s="5" t="s">
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="B28" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="C28" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="D28" s="5" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" ht="75" x14ac:dyDescent="0.25">
-      <c r="A29" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="C29" s="5" t="s">
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="C29" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="D29" s="5" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="C30" s="5" t="s">
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="B30" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="C30" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="D30" s="5" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="C31" s="5" t="s">
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="B31" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="C31" s="8" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="C32" s="5" t="s">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="B32" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="C32" s="8" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="C33" s="5" t="s">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="B33" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="C33" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="D33" s="5" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="C34" s="5" t="s">
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="B34" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="C34" s="8" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="C35" s="5" t="s">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="B35" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="C35" s="8" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="C36" s="5" t="s">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="B36" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="C36" s="8" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="C37" s="5" t="s">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="B37" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="C37" s="8" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="C38" s="5" t="s">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="B38" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="C38" s="8" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="C39" s="5" t="s">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="B39" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="C39" s="8" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="C40" s="5" t="s">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="B40" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="C40" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="D40" s="5" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A41" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="C41" s="5" t="s">
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="B41" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="C41" s="8" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A42" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="C42" s="5" t="s">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="B42" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="C42" s="8" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A43" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="C43" s="5" t="s">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="B43" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="C43" s="8" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A44" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="C44" s="5" t="s">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="B44" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="C44" s="8" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A45" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="C45" s="5" t="s">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="B45" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="C45" s="8" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A46" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="C46" s="5" t="s">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="B46" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="C46" s="8" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A47" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="C47" s="5" t="s">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="B47" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="C47" s="8" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A48" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="C48" s="5" t="s">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="B48" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="C48" s="8" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="C49" s="5" t="s">
+      <c r="A49" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="B49" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="C49" s="8" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="C50" s="5" t="s">
+      <c r="A50" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="B50" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="C50" s="8" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="B51" s="5" t="s">
+      <c r="A51" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="B51" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="C51" s="5" t="s">
+      <c r="C51" s="8" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="B52" s="5" t="s">
+      <c r="A52" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="B52" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="C52" s="5" t="s">
+      <c r="C52" s="8" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="B53" s="5" t="s">
+      <c r="A53" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="B53" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="C53" s="5" t="s">
+      <c r="C53" s="8" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A54" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="B54" s="5" t="s">
+      <c r="A54" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="B54" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="C54" s="5" t="s">
+      <c r="C54" s="8" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A55" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="B55" s="5" t="s">
+      <c r="A55" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="B55" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="C55" s="5" t="s">
+      <c r="C55" s="8" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="B56" s="5" t="s">
+      <c r="A56" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="B56" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="C56" s="5" t="s">
+      <c r="C56" s="8" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="B57" s="5" t="s">
+      <c r="A57" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="B57" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="C57" s="5" t="s">
+      <c r="C57" s="8" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="B58" s="5" t="s">
+      <c r="A58" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="B58" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="C58" s="5" t="s">
+      <c r="C58" s="8" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A59" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="B59" s="5" t="s">
+      <c r="A59" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="B59" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="C59" s="5" t="s">
+      <c r="C59" s="8" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A60" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="B60" s="5" t="s">
+      <c r="A60" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="B60" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="C60" s="5" t="s">
+      <c r="C60" s="8" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A61" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="B61" s="5" t="s">
+      <c r="A61" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="B61" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="C61" s="5" t="s">
+      <c r="C61" s="8" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A62" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="B62" s="5" t="s">
+      <c r="A62" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="B62" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="C62" s="5" t="s">
+      <c r="C62" s="8" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A63" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="B63" s="5" t="s">
+      <c r="A63" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="B63" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="C63" s="5" t="s">
+      <c r="C63" s="8" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A64" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="B64" s="5" t="s">
+      <c r="A64" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="B64" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="C64" s="5" t="s">
+      <c r="C64" s="8" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A65" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="B65" s="5" t="s">
+      <c r="A65" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="B65" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="C65" s="5" t="s">
+      <c r="C65" s="8" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A66" s="4" t="s">
+      <c r="A66" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="B66" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="C66" s="5" t="s">
+      <c r="B66" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="C66" s="8" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A67" s="4" t="s">
+      <c r="A67" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="B67" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="C67" s="5" t="s">
+      <c r="B67" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="C67" s="8" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A68" s="4" t="s">
+      <c r="A68" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="B68" s="5" t="s">
+      <c r="B68" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="C68" s="5" t="s">
+      <c r="C68" s="8" t="s">
         <v>82</v>
       </c>
     </row>

--- a/Files List Error Tracking.xlsx
+++ b/Files List Error Tracking.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AppDev\DebitLens\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{63CDCEC1-4EAC-42A0-AFA6-37C4D4DF03E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{F761D444-B068-4133-BB58-4407AFA0D087}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" activeTab="1" xr2:uid="{0EC2DA8C-4978-4A72-B938-F974F5269E45}"/>
   </bookViews>
   <sheets>
     <sheet name="Error List" sheetId="2" r:id="rId1"/>
     <sheet name="Files List" sheetId="1" r:id="rId2"/>
+    <sheet name="ChatGPT Software Dev List" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
@@ -43,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="116">
   <si>
     <t>AccountForm.tsx"</t>
   </si>
@@ -307,12 +308,99 @@
   </si>
   <si>
     <t>Errors</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Title</t>
+  </si>
+  <si>
+    <t>Improvement options post-baseline</t>
+  </si>
+  <si>
+    <t>Error list review</t>
+  </si>
+  <si>
+    <t>DataExportImportScreen code</t>
+  </si>
+  <si>
+    <t>Complete CSV export</t>
+  </si>
+  <si>
+    <t>Export button Implementation</t>
+  </si>
+  <si>
+    <t>CSV import fix</t>
+  </si>
+  <si>
+    <t>Phase 3 RecurringScreen</t>
+  </si>
+  <si>
+    <t>Phase 3 reconstruction options</t>
+  </si>
+  <si>
+    <t>Phase 3 scope plan</t>
+  </si>
+  <si>
+    <t>Roadmap options list</t>
+  </si>
+  <si>
+    <t>Platform for code placement</t>
+  </si>
+  <si>
+    <t>Unity 2d Training</t>
+  </si>
+  <si>
+    <t>Game creash troubleshooting</t>
+  </si>
+  <si>
+    <t>Cricket CommentaryLabel warning</t>
+  </si>
+  <si>
+    <t>Dice Cricket Game</t>
+  </si>
+  <si>
+    <t>Coin flick animation</t>
+  </si>
+  <si>
+    <t>Commentary system structure</t>
+  </si>
+  <si>
+    <t>Dice Cricket Game Plan</t>
+  </si>
+  <si>
+    <t>Best Platformfor 2D Games</t>
+  </si>
+  <si>
+    <t>CricketDiceGame</t>
+  </si>
+  <si>
+    <t>ProjectCheckList</t>
+  </si>
+  <si>
+    <t>SwiftUI Visual Checklist</t>
+  </si>
+  <si>
+    <t>JSON keyNotFound error fix</t>
+  </si>
+  <si>
+    <t>backup.ts</t>
+  </si>
+  <si>
+    <t>backupReminder.ts</t>
+  </si>
+  <si>
+    <t>BackupRestoreScreen.tsx</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="165" formatCode="dd/mm/yyyy;@"/>
+  </numFmts>
   <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -796,7 +884,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -820,6 +908,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1234,7 +1324,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B41C8E12-756B-4D03-AF8C-7EAD0401066F}">
-  <dimension ref="A1:D68"/>
+  <dimension ref="A1:D71"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.7109375" style="8" bestFit="1" customWidth="1"/>
@@ -1563,7 +1653,7 @@
         <v>65</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>27</v>
+        <v>115</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
@@ -1574,7 +1664,7 @@
         <v>65</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
@@ -1585,7 +1675,7 @@
         <v>65</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
@@ -1596,7 +1686,7 @@
         <v>65</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
@@ -1607,7 +1697,7 @@
         <v>65</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
@@ -1618,7 +1708,7 @@
         <v>65</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
@@ -1629,7 +1719,7 @@
         <v>65</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
@@ -1640,7 +1730,7 @@
         <v>65</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
@@ -1651,7 +1741,7 @@
         <v>65</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
@@ -1662,7 +1752,7 @@
         <v>65</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
@@ -1673,7 +1763,7 @@
         <v>65</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
@@ -1684,7 +1774,7 @@
         <v>65</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
@@ -1695,7 +1785,7 @@
         <v>65</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
@@ -1706,7 +1796,7 @@
         <v>65</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
@@ -1717,7 +1807,7 @@
         <v>65</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
@@ -1728,7 +1818,7 @@
         <v>65</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
@@ -1739,7 +1829,7 @@
         <v>65</v>
       </c>
       <c r="C45" s="8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
@@ -1750,7 +1840,7 @@
         <v>65</v>
       </c>
       <c r="C46" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
@@ -1761,7 +1851,7 @@
         <v>65</v>
       </c>
       <c r="C47" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
@@ -1772,7 +1862,7 @@
         <v>65</v>
       </c>
       <c r="C48" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
@@ -1783,7 +1873,7 @@
         <v>65</v>
       </c>
       <c r="C49" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
@@ -1794,7 +1884,7 @@
         <v>65</v>
       </c>
       <c r="C50" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
@@ -1802,10 +1892,10 @@
         <v>78</v>
       </c>
       <c r="B51" s="8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C51" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
@@ -1816,7 +1906,7 @@
         <v>66</v>
       </c>
       <c r="C52" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
@@ -1824,10 +1914,10 @@
         <v>78</v>
       </c>
       <c r="B53" s="8" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C53" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
@@ -1835,10 +1925,10 @@
         <v>78</v>
       </c>
       <c r="B54" s="8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C54" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
@@ -1849,7 +1939,7 @@
         <v>68</v>
       </c>
       <c r="C55" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
@@ -1860,7 +1950,7 @@
         <v>68</v>
       </c>
       <c r="C56" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
@@ -1871,7 +1961,7 @@
         <v>68</v>
       </c>
       <c r="C57" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
@@ -1879,10 +1969,10 @@
         <v>78</v>
       </c>
       <c r="B58" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C58" s="8" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
@@ -1893,7 +1983,7 @@
         <v>69</v>
       </c>
       <c r="C59" s="8" t="s">
-        <v>71</v>
+        <v>113</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
@@ -1904,7 +1994,7 @@
         <v>69</v>
       </c>
       <c r="C60" s="8" t="s">
-        <v>72</v>
+        <v>114</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
@@ -1915,7 +2005,7 @@
         <v>69</v>
       </c>
       <c r="C61" s="8" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
@@ -1926,7 +2016,7 @@
         <v>69</v>
       </c>
       <c r="C62" s="8" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
@@ -1937,7 +2027,7 @@
         <v>69</v>
       </c>
       <c r="C63" s="8" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
@@ -1948,7 +2038,7 @@
         <v>69</v>
       </c>
       <c r="C64" s="8" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
@@ -1959,40 +2049,280 @@
         <v>69</v>
       </c>
       <c r="C65" s="8" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" s="7" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B66" s="8" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="C66" s="8" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B67" s="8" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="C67" s="8" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="B68" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="C68" s="8" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="B69" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="C69" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="B70" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="C70" s="8" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="B68" s="8" t="s">
+      <c r="B71" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="C68" s="8" t="s">
+      <c r="C71" s="8" t="s">
         <v>82</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B81775CC-3C2F-4602-8884-45EFEDEA5354}">
+  <dimension ref="A1:B24"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="10.42578125" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="64.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="10">
+        <v>46006</v>
+      </c>
+      <c r="B2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="10">
+        <v>46006</v>
+      </c>
+      <c r="B3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="10">
+        <v>46001</v>
+      </c>
+      <c r="B4" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="10">
+        <v>46000</v>
+      </c>
+      <c r="B5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="10">
+        <v>45999</v>
+      </c>
+      <c r="B6" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="10">
+        <v>45995</v>
+      </c>
+      <c r="B7" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="10">
+        <v>45985</v>
+      </c>
+      <c r="B8" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="10">
+        <v>46007</v>
+      </c>
+      <c r="B9" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="10">
+        <v>45971</v>
+      </c>
+      <c r="B10" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="10">
+        <v>45964</v>
+      </c>
+      <c r="B11" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="10">
+        <v>45964</v>
+      </c>
+      <c r="B12" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="10">
+        <v>45964</v>
+      </c>
+      <c r="B13" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="10">
+        <v>45929</v>
+      </c>
+      <c r="B14" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="10">
+        <v>45893</v>
+      </c>
+      <c r="B15" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="10">
+        <v>45887</v>
+      </c>
+      <c r="B16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="10">
+        <v>45887</v>
+      </c>
+      <c r="B17" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="10">
+        <v>45877</v>
+      </c>
+      <c r="B18" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="10">
+        <v>45856</v>
+      </c>
+      <c r="B19" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="10">
+        <v>45856</v>
+      </c>
+      <c r="B20" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="10">
+        <v>45855</v>
+      </c>
+      <c r="B21" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="10">
+        <v>45846</v>
+      </c>
+      <c r="B22" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" s="10">
+        <v>45844</v>
+      </c>
+      <c r="B23" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="10">
+        <v>45842</v>
+      </c>
+      <c r="B24" t="s">
+        <v>112</v>
       </c>
     </row>
   </sheetData>

--- a/Files List Error Tracking.xlsx
+++ b/Files List Error Tracking.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AppDev\DebitLens\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{F761D444-B068-4133-BB58-4407AFA0D087}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{42EEFD91-A917-4FE6-BA46-A47CBC037440}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" activeTab="1" xr2:uid="{0EC2DA8C-4978-4A72-B938-F974F5269E45}"/>
+    <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" activeTab="3" xr2:uid="{0EC2DA8C-4978-4A72-B938-F974F5269E45}"/>
   </bookViews>
   <sheets>
     <sheet name="Error List" sheetId="2" r:id="rId1"/>
     <sheet name="Files List" sheetId="1" r:id="rId2"/>
     <sheet name="ChatGPT Software Dev List" sheetId="3" r:id="rId3"/>
+    <sheet name="Development Streams" sheetId="5" r:id="rId4"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
@@ -44,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="197">
   <si>
     <t>AccountForm.tsx"</t>
   </si>
@@ -52,9 +53,6 @@
     <t>ActionFab.tsx"</t>
   </si>
   <si>
-    <t>BalanceCard.tsx</t>
-  </si>
-  <si>
     <t>Center.tsx</t>
   </si>
   <si>
@@ -64,9 +62,6 @@
     <t>LineChart.tsx"</t>
   </si>
   <si>
-    <t>PaymentCard.tsx</t>
-  </si>
-  <si>
     <t>PaymentForm.tsx"</t>
   </si>
   <si>
@@ -76,9 +71,6 @@
     <t>ReportChart.tsx"</t>
   </si>
   <si>
-    <t>UpcomingTimeline.tsx"</t>
-  </si>
-  <si>
     <t>db.ts</t>
   </si>
   <si>
@@ -142,18 +134,12 @@
     <t>HistoryScreen.tsx"</t>
   </si>
   <si>
-    <t>HomeScreen.tsx</t>
-  </si>
-  <si>
     <t>ImportCsvScreen.tsx"</t>
   </si>
   <si>
     <t>LoginScreen.tsx</t>
   </si>
   <si>
-    <t>NavigationsScreen.tsx"</t>
-  </si>
-  <si>
     <t>NotificationsScreen.tsx"</t>
   </si>
   <si>
@@ -283,12 +269,6 @@
     <t>src</t>
   </si>
   <si>
-    <t>HookSmokeTest.tsx</t>
-  </si>
-  <si>
-    <t>TestReact.tsx</t>
-  </si>
-  <si>
     <t>DebitLens</t>
   </si>
   <si>
@@ -385,6 +365,153 @@
     <t>JSON keyNotFound error fix</t>
   </si>
   <si>
+    <t>Stable navigation</t>
+  </si>
+  <si>
+    <t>Accounts &amp; Transactions CRUD</t>
+  </si>
+  <si>
+    <t>CSV export working</t>
+  </si>
+  <si>
+    <t>CSV import functional</t>
+  </si>
+  <si>
+    <t>Cleaned screen structure</t>
+  </si>
+  <si>
+    <t>No reducer complexity (intentional)</t>
+  </si>
+  <si>
+    <t>Option 1 — Data Safety &amp; Trust (Recommended First)</t>
+  </si>
+  <si>
+    <t>Restore replaces state cleanly</t>
+  </si>
+  <si>
+    <t>Show counts: transactions, accounts</t>
+  </si>
+  <si>
+    <t>Imported / skipped / merged counts</t>
+  </si>
+  <si>
+    <t>DataExportImportScreen</t>
+  </si>
+  <si>
+    <t>Minimal UI additions</t>
+  </si>
+  <si>
+    <t>Option 2 — Reporting &amp; Insight (High User Value)</t>
+  </si>
+  <si>
+    <t>Monthly pie or bar chart</t>
+  </si>
+  <si>
+    <t>Expenses over time</t>
+  </si>
+  <si>
+    <t>Option 3 — Recurring Transactions (Lifecycle Feature)</t>
+  </si>
+  <si>
+    <t>Generator utility</t>
+  </si>
+  <si>
+    <t>RecurringScreen</t>
+  </si>
+  <si>
+    <t>Option 4 — Rules Engine (Automation Layer)</t>
+  </si>
+  <si>
+    <t>“If amount &gt; £500 → Flag as Large Expense”</t>
+  </si>
+  <si>
+    <t>“If transfer → Auto-hide from reports”</t>
+  </si>
+  <si>
+    <t>Rules evaluation utility</t>
+  </si>
+  <si>
+    <t>Transaction post-processing hook</t>
+  </si>
+  <si>
+    <t>Simple Rules UI</t>
+  </si>
+  <si>
+    <t>Option 5 — Budgeting &amp; Alerts</t>
+  </si>
+  <si>
+    <t>Monthly budgets by category</t>
+  </si>
+  <si>
+    <t>Progress bars</t>
+  </si>
+  <si>
+    <t>Optional push notifications (later)</t>
+  </si>
+  <si>
+    <t>Budgets state</t>
+  </si>
+  <si>
+    <t>Category aggregation helpers</t>
+  </si>
+  <si>
+    <t>Dashboard UI additions</t>
+  </si>
+  <si>
+    <t>Option 6 — UX Polish &amp; Productivity</t>
+  </si>
+  <si>
+    <t>Undo delete (snackbar)</t>
+  </si>
+  <si>
+    <t>Mostly UI components</t>
+  </si>
+  <si>
+    <t>Very low data-risk</t>
+  </si>
+  <si>
+    <t>Option 7 — Persistence &amp; Scale (Later Phase)</t>
+  </si>
+  <si>
+    <t>SQLite persistence</t>
+  </si>
+  <si>
+    <t>Background sync preparation</t>
+  </si>
+  <si>
+    <t>Cloud backup hooks (future)</t>
+  </si>
+  <si>
+    <t>Multi-currency groundwork</t>
+  </si>
+  <si>
+    <t>Working AppProvider / useApp</t>
+  </si>
+  <si>
+    <t>Everything below builds on this, not replaces it.</t>
+  </si>
+  <si>
+    <t>One-tap export of entire app state</t>
+  </si>
+  <si>
+    <t>AppContext (safe replace helper)</t>
+  </si>
+  <si>
+    <t>New ReportsScreen</t>
+  </si>
+  <si>
+    <t>Selector utilities (getTxsByMonth)</t>
+  </si>
+  <si>
+    <t>Extend AppState (recurring[])</t>
+  </si>
+  <si>
+    <t>“If description contains Tesco → Category = Groceries”</t>
+  </si>
+  <si>
+    <t>Baseline (Confirmed)</t>
+  </si>
+  <si>
     <t>backup.ts</t>
   </si>
   <si>
@@ -392,6 +519,123 @@
   </si>
   <si>
     <t>BackupRestoreScreen.tsx</t>
+  </si>
+  <si>
+    <t>Link 1</t>
+  </si>
+  <si>
+    <t>SplashAuthScreen, DataExportImportScreen, DashboardScreen, PaymentsScreen, TransferScreen, TxnEditorScreen, RecentActivityScreen, BudgetsScreen, ImportCsvScreen, ReportsScreen, NotificationsScreen, AccountScreen, ReccuringScreen, RecurringEditorScreen, SettingsScreen</t>
+  </si>
+  <si>
+    <t>AppContext</t>
+  </si>
+  <si>
+    <t>AppContext, backupReminder, types</t>
+  </si>
+  <si>
+    <t>SplashAuthScreen, types</t>
+  </si>
+  <si>
+    <t>AppContext, types</t>
+  </si>
+  <si>
+    <t>AppContext, backup, types</t>
+  </si>
+  <si>
+    <t>AppContext, formatDate</t>
+  </si>
+  <si>
+    <t>AppContext, types, formatDate</t>
+  </si>
+  <si>
+    <t>backup, reporting</t>
+  </si>
+  <si>
+    <t>db, reporting</t>
+  </si>
+  <si>
+    <t>finance, reportUtils</t>
+  </si>
+  <si>
+    <t>resetDb</t>
+  </si>
+  <si>
+    <t>Completed</t>
+  </si>
+  <si>
+    <t>YES</t>
+  </si>
+  <si>
+    <t>Full Backup / Restore (JSON)</t>
+  </si>
+  <si>
+    <t>Import Preview + Validation</t>
+  </si>
+  <si>
+    <t>Warn On: Missing accounts</t>
+  </si>
+  <si>
+    <t>Warn On: Invalid dates / amounts</t>
+  </si>
+  <si>
+    <t>Last Backup Status</t>
+  </si>
+  <si>
+    <t>Import Result Summary</t>
+  </si>
+  <si>
+    <t>Lightweight chart lib (Victory already explored</t>
+  </si>
+  <si>
+    <t>Spending by Category</t>
+  </si>
+  <si>
+    <t>Monthly / Weekly Trends</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Income vs Expense Summary</t>
+  </si>
+  <si>
+    <t>Top 5 Categories / Merchants</t>
+  </si>
+  <si>
+    <t>Recurring definitions (weekly, monthly)</t>
+  </si>
+  <si>
+    <t>Auto-generate upcoming transactions</t>
+  </si>
+  <si>
+    <t>Edit series vs single occurrence</t>
+  </si>
+  <si>
+    <t>Preview future impact on balances</t>
+  </si>
+  <si>
+    <t>Warnings: “You’re at 90% of Groceries budget”</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Search transactions</t>
+  </si>
+  <si>
+    <t>Quick category reassignment</t>
+  </si>
+  <si>
+    <t>Sort by amount/date</t>
+  </si>
+  <si>
+    <t>Inline edit</t>
+  </si>
+  <si>
+    <t>Favourite categories</t>
+  </si>
+  <si>
+    <t>Development Order</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Improvement Description</t>
   </si>
 </sst>
 </file>
@@ -401,7 +645,7 @@
   <numFmts count="1">
     <numFmt numFmtId="165" formatCode="dd/mm/yyyy;@"/>
   </numFmts>
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -532,6 +776,12 @@
     <font>
       <sz val="11"/>
       <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -884,7 +1134,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -910,6 +1160,15 @@
     </xf>
     <xf numFmtId="165" fontId="0" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1285,7 +1544,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C0B799D-B152-4EDC-90BC-C1450490B7CC}">
-  <dimension ref="A2:D17"/>
+  <dimension ref="A2:E17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
@@ -1294,9 +1553,9 @@
     <col min="4" max="4" width="114.5703125" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="str" cm="1">
-        <f t="array" ref="A2:D2">_xlfn._xlws.FILTER('Files List'!A:D, 'Files List'!D:D&lt;&gt;"")</f>
+        <f t="array" ref="A2:E2">_xlfn._xlws.FILTER('Files List'!A:E, 'Files List'!E:E&lt;&gt;"")</f>
         <v>Root Folder</v>
       </c>
       <c r="B2" s="2" t="str">
@@ -1306,16 +1565,19 @@
         <v>Files</v>
       </c>
       <c r="D2" s="2" t="str">
+        <v>Link 1</v>
+      </c>
+      <c r="E2" t="str">
         <v>Errors</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="30" x14ac:dyDescent="0.25"/>
-    <row r="4" spans="1:4" ht="30" x14ac:dyDescent="0.25"/>
-    <row r="7" spans="1:4" ht="75" x14ac:dyDescent="0.25"/>
-    <row r="11" spans="1:4" ht="120" x14ac:dyDescent="0.25"/>
-    <row r="12" spans="1:4" ht="150" x14ac:dyDescent="0.25"/>
-    <row r="15" spans="1:4" ht="30" x14ac:dyDescent="0.25"/>
-    <row r="16" spans="1:4" ht="30" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="1:5" ht="30" x14ac:dyDescent="0.25"/>
+    <row r="4" spans="1:5" ht="30" x14ac:dyDescent="0.25"/>
+    <row r="7" spans="1:5" ht="75" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="1:5" ht="120" x14ac:dyDescent="0.25"/>
+    <row r="12" spans="1:5" ht="150" x14ac:dyDescent="0.25"/>
+    <row r="15" spans="1:5" ht="30" x14ac:dyDescent="0.25"/>
+    <row r="16" spans="1:5" ht="30" x14ac:dyDescent="0.25"/>
     <row r="17" ht="60" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1324,801 +1586,801 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B41C8E12-756B-4D03-AF8C-7EAD0401066F}">
-  <dimension ref="A1:D71"/>
+  <dimension ref="A1:E64"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.7109375" style="8" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="21.7109375" style="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27.140625" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="73.5703125" style="8" customWidth="1"/>
-    <col min="5" max="16384" width="9.140625" style="6"/>
+    <col min="4" max="4" width="24.85546875" style="8" customWidth="1"/>
+    <col min="5" max="5" width="73.5703125" style="8" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+        <v>158</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="C2" s="8" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="C4" s="8" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="C5" s="8" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="C6" s="8" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="C7" s="8" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="C8" s="8" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="C9" s="8" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D9" s="8" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C10" s="8" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C11" s="8" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D11" s="8" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C12" s="8" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C13" s="8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C14" s="8" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C15" s="8" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C16" s="8" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C17" s="8" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" ht="225" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C18" s="8" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D18" s="8" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C19" s="8" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="C20" s="8" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C21" s="8" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C22" s="8" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C23" s="8" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D23" s="8" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C24" s="8" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D24" s="8" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C25" s="8" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D25" s="8" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C26" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="D26" s="8" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="C27" s="8" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="B27" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="C27" s="8" t="s">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="B28" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="C28" s="8" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="B28" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="C28" s="8" t="s">
+      <c r="D28" s="8" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="C29" s="8" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="B29" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="C29" s="8" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D29" s="8" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C30" s="8" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D30" s="8" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C31" s="8" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D31" s="8" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="7" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C32" s="8" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C33" s="8" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D33" s="8" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="7" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C34" s="8" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C35" s="8" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D35" s="8" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="7" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C36" s="8" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D36" s="8" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C37" s="8" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="7" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C38" s="8" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D38" s="8" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C39" s="8" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D39" s="8" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="7" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C40" s="8" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D40" s="8" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C41" s="8" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D41" s="8" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A42" s="7" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C42" s="8" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D42" s="8" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C43" s="8" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D43" s="8" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="7" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C44" s="8" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D44" s="8" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C45" s="8" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D45" s="8" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="7" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B46" s="8" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C46" s="8" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C47" s="8" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D47" s="8" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="7" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B48" s="8" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C48" s="8" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B49" s="8" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C49" s="8" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="7" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B50" s="8" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C50" s="8" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B51" s="8" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C51" s="8" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="7" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B52" s="8" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C52" s="8" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B53" s="8" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C53" s="8" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="7" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B54" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="C54" s="8" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A55" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="B55" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="C55" s="8" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="B56" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="C56" s="8" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A57" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="B57" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="C57" s="8" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A58" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="B58" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="C58" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="C54" s="8" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A55" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="B55" s="8" t="s">
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A59" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="B59" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="C59" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="C55" s="8" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="B56" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="C56" s="8" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="B57" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="C57" s="8" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="B58" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="C58" s="8" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A59" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="B59" s="8" t="s">
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A60" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="B60" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="C60" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="C59" s="8" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A60" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="B60" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="C60" s="8" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B61" s="8" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="C61" s="8" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" s="7" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B62" s="8" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="C62" s="8" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D62" s="8" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B63" s="8" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="C63" s="8" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" s="7" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B64" s="8" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="C64" s="8" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A65" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="B65" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="C65" s="8" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A66" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="B66" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="C66" s="8" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A67" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="B67" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="C67" s="8" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A68" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="B68" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="C68" s="8" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A69" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="B69" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="C69" s="8" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A70" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="B70" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="C70" s="8" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A71" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="B71" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="C71" s="8" t="s">
-        <v>82</v>
-      </c>
-    </row>
   </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -2135,10 +2397,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -2146,7 +2408,7 @@
         <v>46006</v>
       </c>
       <c r="B2" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -2154,7 +2416,7 @@
         <v>46006</v>
       </c>
       <c r="B3" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -2162,7 +2424,7 @@
         <v>46001</v>
       </c>
       <c r="B4" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -2170,7 +2432,7 @@
         <v>46000</v>
       </c>
       <c r="B5" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -2178,7 +2440,7 @@
         <v>45999</v>
       </c>
       <c r="B6" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -2186,7 +2448,7 @@
         <v>45995</v>
       </c>
       <c r="B7" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -2194,7 +2456,7 @@
         <v>45985</v>
       </c>
       <c r="B8" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -2202,7 +2464,7 @@
         <v>46007</v>
       </c>
       <c r="B9" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -2210,7 +2472,7 @@
         <v>45971</v>
       </c>
       <c r="B10" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -2218,7 +2480,7 @@
         <v>45964</v>
       </c>
       <c r="B11" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -2226,7 +2488,7 @@
         <v>45964</v>
       </c>
       <c r="B12" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -2234,7 +2496,7 @@
         <v>45964</v>
       </c>
       <c r="B13" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -2242,7 +2504,7 @@
         <v>45929</v>
       </c>
       <c r="B14" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -2250,7 +2512,7 @@
         <v>45893</v>
       </c>
       <c r="B15" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -2258,7 +2520,7 @@
         <v>45887</v>
       </c>
       <c r="B16" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -2266,7 +2528,7 @@
         <v>45887</v>
       </c>
       <c r="B17" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -2274,7 +2536,7 @@
         <v>45877</v>
       </c>
       <c r="B18" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -2282,7 +2544,7 @@
         <v>45856</v>
       </c>
       <c r="B19" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -2290,7 +2552,7 @@
         <v>45856</v>
       </c>
       <c r="B20" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
@@ -2298,7 +2560,7 @@
         <v>45855</v>
       </c>
       <c r="B21" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -2306,7 +2568,7 @@
         <v>45846</v>
       </c>
       <c r="B22" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
@@ -2314,7 +2576,7 @@
         <v>45844</v>
       </c>
       <c r="B23" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
@@ -2322,7 +2584,748 @@
         <v>45842</v>
       </c>
       <c r="B24" t="s">
+        <v>105</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{765FA9AB-2F58-4BF3-9F12-CF3ACC6AC4D6}">
+  <dimension ref="A1:D63"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="13.28515625" style="12" customWidth="1"/>
+    <col min="2" max="2" width="47.85546875" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="49.140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5703125" style="6" customWidth="1"/>
+    <col min="5" max="16384" width="9.140625" style="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" s="8" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1" s="11" t="s">
+        <v>194</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="12">
+        <v>0.01</v>
+      </c>
+      <c r="B2" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="12">
+        <v>0.02</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="12">
+        <v>0.03</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="12">
+        <v>0.04</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="12">
+        <v>0.05</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="12">
+        <v>0.06</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="12">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="12">
+        <v>0.08</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="12">
+        <v>1.01</v>
+      </c>
+      <c r="B10" s="6" t="s">
         <v>112</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="12">
+        <v>1.02</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="12">
+        <v>1.03</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="12">
+        <v>1.04</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="12">
+        <v>1.05</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="12">
+        <v>1.06</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="12">
+        <v>1.07</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="12">
+        <v>1.08</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="12">
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="12">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="12">
+        <v>1.1100000000000001</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="12">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="12">
+        <v>1.1299999999999999</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="12">
+        <v>2.0099999999999998</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" s="12">
+        <v>2.02</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="12">
+        <v>2.0299999999999998</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="12">
+        <v>2.04</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="12">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="12">
+        <v>2.06</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="12">
+        <v>2.0699999999999998</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" s="12">
+        <v>2.08</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="12">
+        <v>2.09</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" s="12">
+        <v>4.01</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" s="12">
+        <v>4.0199999999999996</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" s="12">
+        <v>4.03</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" s="12">
+        <v>4.04</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" s="12">
+        <v>4.05</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" s="12">
+        <v>4.0599999999999996</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" s="12">
+        <v>4.07</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" s="12">
+        <v>5.01</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" s="12">
+        <v>5.0199999999999996</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" s="12">
+        <v>5.03</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" s="12">
+        <v>5.04</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="C42" s="6" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" s="12">
+        <v>5.05</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="C43" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" s="12">
+        <v>5.0599999999999996</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="C44" s="6" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" s="12">
+        <v>6.01</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="C45" s="6" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" s="12">
+        <v>6.02</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="C46" s="6" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" s="12">
+        <v>6.03</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="C47" s="6" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" s="12">
+        <v>6.04</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="C48" s="6" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" s="12">
+        <v>6.05</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="C49" s="6" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" s="12">
+        <v>6.06</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="C50" s="6" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" s="12">
+        <v>6.07</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="C51" s="6" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" s="12">
+        <v>5.01</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="C52" s="6" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" s="12">
+        <v>5.0199999999999996</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="C53" s="6" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" s="12">
+        <v>5.03</v>
+      </c>
+      <c r="B54" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="C54" s="6" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" s="12">
+        <v>5.04</v>
+      </c>
+      <c r="B55" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="C55" s="6" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" s="12">
+        <v>5.05</v>
+      </c>
+      <c r="B56" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="C56" s="6" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" s="12">
+        <v>5.0599999999999996</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="C57" s="6" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" s="12">
+        <v>5.07</v>
+      </c>
+      <c r="B58" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="C58" s="6" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" s="12">
+        <v>5.08</v>
+      </c>
+      <c r="B59" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="C59" s="6" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" s="12">
+        <v>7.01</v>
+      </c>
+      <c r="B60" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="C60" s="6" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" s="12">
+        <v>7.02</v>
+      </c>
+      <c r="B61" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="C61" s="6" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" s="12">
+        <v>7.03</v>
+      </c>
+      <c r="B62" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="C62" s="6" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" s="12">
+        <v>7.04</v>
+      </c>
+      <c r="B63" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="C63" s="6" t="s">
+        <v>145</v>
       </c>
     </row>
   </sheetData>

--- a/Files List Error Tracking.xlsx
+++ b/Files List Error Tracking.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AppDev\DebitLens\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{42EEFD91-A917-4FE6-BA46-A47CBC037440}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{F5078690-8059-4CE2-9B10-4D1DA1228A52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" activeTab="3" xr2:uid="{0EC2DA8C-4978-4A72-B938-F974F5269E45}"/>
+    <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" activeTab="1" xr2:uid="{0EC2DA8C-4978-4A72-B938-F974F5269E45}"/>
   </bookViews>
   <sheets>
     <sheet name="Error List" sheetId="2" r:id="rId1"/>
@@ -18,6 +18,9 @@
     <sheet name="ChatGPT Software Dev List" sheetId="3" r:id="rId3"/>
     <sheet name="Development Streams" sheetId="5" r:id="rId4"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'ChatGPT Software Dev List'!$A$1:$B$29</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
@@ -45,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="204">
   <si>
     <t>AccountForm.tsx"</t>
   </si>
@@ -524,9 +527,6 @@
     <t>Link 1</t>
   </si>
   <si>
-    <t>SplashAuthScreen, DataExportImportScreen, DashboardScreen, PaymentsScreen, TransferScreen, TxnEditorScreen, RecentActivityScreen, BudgetsScreen, ImportCsvScreen, ReportsScreen, NotificationsScreen, AccountScreen, ReccuringScreen, RecurringEditorScreen, SettingsScreen</t>
-  </si>
-  <si>
     <t>AppContext</t>
   </si>
   <si>
@@ -636,6 +636,30 @@
   </si>
   <si>
     <t>Improvement Description</t>
+  </si>
+  <si>
+    <t>File usage mapping</t>
+  </si>
+  <si>
+    <t>Option 2 Implementationplan</t>
+  </si>
+  <si>
+    <t>BudgetEditorScreen.tsk</t>
+  </si>
+  <si>
+    <t>Reports polish complete</t>
+  </si>
+  <si>
+    <t>Build Requirement 6</t>
+  </si>
+  <si>
+    <t>SplashAuthScreen, DataExportImportScreen, DashboardScreen, PaymentsScreen, TransferScreen, TxnEditorScreen, RecentActivityScreen, BudgetEditorScreen, BudgetsScreen, ImportCsvScreen, ReportsScreen, NotificationsScreen, AccountScreen, ReccuringScreen, RecurringEditorScreen, SettingsScreen</t>
+  </si>
+  <si>
+    <t>Next steps discussion</t>
+  </si>
+  <si>
+    <t>PaymentEditorScreen.tsx</t>
   </si>
 </sst>
 </file>
@@ -1586,7 +1610,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B41C8E12-756B-4D03-AF8C-7EAD0401066F}">
-  <dimension ref="A1:E64"/>
+  <dimension ref="A1:E66"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.7109375" style="8" bestFit="1" customWidth="1"/>
@@ -1702,7 +1726,7 @@
         <v>7</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -1796,7 +1820,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="225" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" ht="240" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
         <v>73</v>
       </c>
@@ -1807,7 +1831,7 @@
         <v>16</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>159</v>
+        <v>201</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1865,7 +1889,7 @@
         <v>21</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -1879,7 +1903,7 @@
         <v>22</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1893,7 +1917,7 @@
         <v>23</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -1907,7 +1931,7 @@
         <v>157</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -1918,7 +1942,10 @@
         <v>60</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>24</v>
+        <v>198</v>
+      </c>
+      <c r="D27" s="8" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -1929,10 +1956,7 @@
         <v>60</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="D28" s="8" t="s">
-        <v>163</v>
+        <v>24</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -1943,10 +1967,10 @@
         <v>60</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1957,10 +1981,10 @@
         <v>60</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>52</v>
+        <v>163</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -1971,10 +1995,10 @@
         <v>60</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>163</v>
+        <v>52</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -1985,7 +2009,10 @@
         <v>60</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -1996,10 +2023,7 @@
         <v>60</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="D33" s="8" t="s">
-        <v>162</v>
+        <v>29</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -2010,7 +2034,10 @@
         <v>60</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>31</v>
+        <v>30</v>
+      </c>
+      <c r="D34" s="8" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -2021,10 +2048,7 @@
         <v>60</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="D35" s="8" t="s">
-        <v>163</v>
+        <v>31</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -2035,10 +2059,10 @@
         <v>60</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>33</v>
+        <v>203</v>
       </c>
       <c r="D36" s="8" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -2049,7 +2073,10 @@
         <v>60</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>34</v>
+        <v>32</v>
+      </c>
+      <c r="D37" s="8" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -2060,13 +2087,13 @@
         <v>60</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D38" s="8" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
         <v>73</v>
       </c>
@@ -2074,10 +2101,7 @@
         <v>60</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="D39" s="8" t="s">
-        <v>166</v>
+        <v>34</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -2088,13 +2112,13 @@
         <v>60</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D40" s="8" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
         <v>73</v>
       </c>
@@ -2102,13 +2126,13 @@
         <v>60</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D41" s="8" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="7" t="s">
         <v>73</v>
       </c>
@@ -2116,7 +2140,7 @@
         <v>60</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D42" s="8" t="s">
         <v>166</v>
@@ -2130,13 +2154,13 @@
         <v>60</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D43" s="8" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A44" s="7" t="s">
         <v>73</v>
       </c>
@@ -2144,13 +2168,13 @@
         <v>60</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D44" s="8" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
         <v>73</v>
       </c>
@@ -2158,10 +2182,10 @@
         <v>60</v>
       </c>
       <c r="C45" s="8" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D45" s="8" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -2172,21 +2196,24 @@
         <v>60</v>
       </c>
       <c r="C46" s="8" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+      <c r="D46" s="8" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
         <v>73</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C47" s="8" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D47" s="8" t="s">
-        <v>52</v>
+        <v>165</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -2194,10 +2221,10 @@
         <v>73</v>
       </c>
       <c r="B48" s="8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C48" s="8" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
@@ -2205,10 +2232,13 @@
         <v>73</v>
       </c>
       <c r="B49" s="8" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C49" s="8" t="s">
-        <v>46</v>
+        <v>44</v>
+      </c>
+      <c r="D49" s="8" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -2216,10 +2246,10 @@
         <v>73</v>
       </c>
       <c r="B50" s="8" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C50" s="8" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
@@ -2227,10 +2257,10 @@
         <v>73</v>
       </c>
       <c r="B51" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C51" s="8" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
@@ -2241,7 +2271,7 @@
         <v>63</v>
       </c>
       <c r="C52" s="8" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
@@ -2252,7 +2282,7 @@
         <v>63</v>
       </c>
       <c r="C53" s="8" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
@@ -2260,10 +2290,10 @@
         <v>73</v>
       </c>
       <c r="B54" s="8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C54" s="8" t="s">
-        <v>155</v>
+        <v>49</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
@@ -2271,10 +2301,10 @@
         <v>73</v>
       </c>
       <c r="B55" s="8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C55" s="8" t="s">
-        <v>156</v>
+        <v>50</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
@@ -2285,7 +2315,7 @@
         <v>64</v>
       </c>
       <c r="C56" s="8" t="s">
-        <v>65</v>
+        <v>155</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
@@ -2296,7 +2326,7 @@
         <v>64</v>
       </c>
       <c r="C57" s="8" t="s">
-        <v>66</v>
+        <v>156</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
@@ -2307,7 +2337,7 @@
         <v>64</v>
       </c>
       <c r="C58" s="8" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
@@ -2318,7 +2348,7 @@
         <v>64</v>
       </c>
       <c r="C59" s="8" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
@@ -2329,7 +2359,7 @@
         <v>64</v>
       </c>
       <c r="C60" s="8" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
@@ -2340,7 +2370,7 @@
         <v>64</v>
       </c>
       <c r="C61" s="8" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
@@ -2351,10 +2381,7 @@
         <v>64</v>
       </c>
       <c r="C62" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="D62" s="8" t="s">
-        <v>169</v>
+        <v>69</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
@@ -2365,17 +2392,42 @@
         <v>64</v>
       </c>
       <c r="C63" s="8" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="B64" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="C64" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="D64" s="8" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="B65" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="C65" s="8" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="B64" s="8" t="s">
+      <c r="B66" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="C64" s="8" t="s">
+      <c r="C66" s="8" t="s">
         <v>75</v>
       </c>
     </row>
@@ -2388,7 +2440,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B81775CC-3C2F-4602-8884-45EFEDEA5354}">
-  <dimension ref="A1:B24"/>
+  <dimension ref="A1:B29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" style="10" bestFit="1" customWidth="1"/>
@@ -2405,90 +2457,90 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10">
-        <v>46006</v>
+        <v>45842</v>
       </c>
       <c r="B2" t="s">
-        <v>83</v>
+        <v>105</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="10">
-        <v>46006</v>
+        <v>45844</v>
       </c>
       <c r="B3" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="10">
-        <v>46001</v>
+        <v>45846</v>
       </c>
       <c r="B4" t="s">
-        <v>85</v>
+        <v>103</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="10">
-        <v>46000</v>
+        <v>45855</v>
       </c>
       <c r="B5" t="s">
-        <v>86</v>
+        <v>102</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="10">
-        <v>45999</v>
+        <v>45856</v>
       </c>
       <c r="B6" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="10">
-        <v>45995</v>
+        <v>45856</v>
       </c>
       <c r="B7" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="10">
-        <v>45985</v>
+        <v>45877</v>
       </c>
       <c r="B8" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="10">
-        <v>46007</v>
+        <v>45887</v>
       </c>
       <c r="B9" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="10">
-        <v>45971</v>
+        <v>45887</v>
       </c>
       <c r="B10" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="10">
-        <v>45964</v>
+        <v>45893</v>
       </c>
       <c r="B11" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="10">
-        <v>45964</v>
+        <v>45929</v>
       </c>
       <c r="B12" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -2496,98 +2548,146 @@
         <v>45964</v>
       </c>
       <c r="B13" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="10">
-        <v>45929</v>
+        <v>45964</v>
       </c>
       <c r="B14" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="10">
-        <v>45893</v>
+        <v>45964</v>
       </c>
       <c r="B15" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="10">
-        <v>45887</v>
+        <v>45971</v>
       </c>
       <c r="B16" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="10">
-        <v>45887</v>
+        <v>45971</v>
       </c>
       <c r="B17" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="10">
-        <v>45877</v>
+        <v>45985</v>
       </c>
       <c r="B18" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="10">
-        <v>45856</v>
+        <v>45995</v>
       </c>
       <c r="B19" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="10">
-        <v>45856</v>
+        <v>45999</v>
       </c>
       <c r="B20" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="10">
-        <v>45855</v>
+        <v>46000</v>
       </c>
       <c r="B21" t="s">
-        <v>102</v>
+        <v>86</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="10">
-        <v>45846</v>
+        <v>46001</v>
       </c>
       <c r="B22" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="10">
-        <v>45844</v>
+        <v>46006</v>
       </c>
       <c r="B23" t="s">
-        <v>104</v>
+        <v>83</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="10">
-        <v>45842</v>
+        <v>46006</v>
       </c>
       <c r="B24" t="s">
-        <v>105</v>
+        <v>84</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="10">
+        <v>46007</v>
+      </c>
+      <c r="B25" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" s="10">
+        <v>46008</v>
+      </c>
+      <c r="B26" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" s="10">
+        <v>46008</v>
+      </c>
+      <c r="B27" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" s="10">
+        <v>46012</v>
+      </c>
+      <c r="B28" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" s="10">
+        <v>46012</v>
+      </c>
+      <c r="B29" t="s">
+        <v>202</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:B29" xr:uid="{B81775CC-3C2F-4602-8884-45EFEDEA5354}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B29">
+      <sortCondition ref="A1:A29"/>
+    </sortState>
+  </autoFilter>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B28">
+    <sortCondition ref="A2:A28"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -2607,16 +2707,16 @@
   <sheetData>
     <row r="1" spans="1:4" s="8" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="B1" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="C1" s="5" t="s">
         <v>195</v>
       </c>
-      <c r="C1" s="5" t="s">
-        <v>196</v>
-      </c>
       <c r="D1" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -2630,7 +2730,7 @@
         <v>106</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -2644,7 +2744,7 @@
         <v>146</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -2658,7 +2758,7 @@
         <v>107</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -2672,7 +2772,7 @@
         <v>108</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -2686,7 +2786,7 @@
         <v>109</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -2700,7 +2800,7 @@
         <v>110</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -2714,7 +2814,7 @@
         <v>111</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -2728,7 +2828,7 @@
         <v>147</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -2739,10 +2839,10 @@
         <v>112</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -2755,6 +2855,9 @@
       <c r="C11" s="6" t="s">
         <v>148</v>
       </c>
+      <c r="D11" s="6" t="s">
+        <v>171</v>
+      </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="12">
@@ -2766,6 +2869,9 @@
       <c r="C12" s="6" t="s">
         <v>113</v>
       </c>
+      <c r="D12" s="6" t="s">
+        <v>171</v>
+      </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="12">
@@ -2775,7 +2881,10 @@
         <v>112</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -2788,6 +2897,9 @@
       <c r="C14" s="6" t="s">
         <v>114</v>
       </c>
+      <c r="D14" s="6" t="s">
+        <v>171</v>
+      </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="12">
@@ -2797,7 +2909,10 @@
         <v>112</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -2808,10 +2923,13 @@
         <v>112</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+        <v>175</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="12">
         <v>1.08</v>
       </c>
@@ -2819,10 +2937,13 @@
         <v>112</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+        <v>176</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="12">
         <v>1.0900000000000001</v>
       </c>
@@ -2830,10 +2951,13 @@
         <v>112</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+        <v>177</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="12">
         <v>1.1000000000000001</v>
       </c>
@@ -2843,8 +2967,11 @@
       <c r="C19" s="6" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D19" s="6" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="12">
         <v>1.1100000000000001</v>
       </c>
@@ -2854,8 +2981,11 @@
       <c r="C20" s="6" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D20" s="6" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="12">
         <v>1.1200000000000001</v>
       </c>
@@ -2865,8 +2995,11 @@
       <c r="C21" s="6" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D21" s="6" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="12">
         <v>1.1299999999999999</v>
       </c>
@@ -2876,8 +3009,11 @@
       <c r="C22" s="6" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D22" s="6" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="12">
         <v>2.0099999999999998</v>
       </c>
@@ -2885,10 +3021,10 @@
         <v>118</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="12">
         <v>2.02</v>
       </c>
@@ -2899,7 +3035,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="12">
         <v>2.0299999999999998</v>
       </c>
@@ -2907,10 +3043,10 @@
         <v>118</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="12">
         <v>2.04</v>
       </c>
@@ -2921,7 +3057,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="12">
         <v>2.0499999999999998</v>
       </c>
@@ -2929,10 +3065,10 @@
         <v>118</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="12">
         <v>2.06</v>
       </c>
@@ -2940,10 +3076,10 @@
         <v>118</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="12">
         <v>2.0699999999999998</v>
       </c>
@@ -2954,7 +3090,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="12">
         <v>2.08</v>
       </c>
@@ -2965,7 +3101,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="12">
         <v>2.09</v>
       </c>
@@ -2973,10 +3109,10 @@
         <v>118</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="12">
         <v>4.01</v>
       </c>
@@ -2984,7 +3120,7 @@
         <v>121</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
@@ -2995,7 +3131,7 @@
         <v>121</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
@@ -3006,7 +3142,7 @@
         <v>121</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
@@ -3017,7 +3153,7 @@
         <v>121</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
@@ -3149,7 +3285,7 @@
         <v>130</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
@@ -3204,7 +3340,7 @@
         <v>137</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
@@ -3215,7 +3351,7 @@
         <v>137</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
@@ -3226,7 +3362,7 @@
         <v>137</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
@@ -3237,7 +3373,7 @@
         <v>137</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
@@ -3248,7 +3384,7 @@
         <v>137</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
